--- a/src/test/resources/Documentation E2E and returns.xlsx
+++ b/src/test/resources/Documentation E2E and returns.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/118f88de5583d5c3/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GOLD\abhitha\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8CE0EE9-759A-41B1-8739-5269E58C9253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2065142D-3198-4E4B-9524-EF23F16C940F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{833F3E32-C531-459D-8391-5D3873C7994A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{833F3E32-C531-459D-8391-5D3873C7994A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -990,7 +991,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1062,4 +1063,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F780C5-0B9E-4093-8FC9-CDE6A4934379}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>